--- a/data/trans_camb/IP13-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP13-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8,72</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6,14</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-1,06</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,65</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-4,6</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-2,33</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8,72</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,14</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,14</t>
+          <t>-1,57</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,66</t>
+          <t>-1,29</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 9,7</t>
+          <t>1,0; 16,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 1,31</t>
+          <t>-1,29; 14,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 4,55</t>
+          <t>-6,04; 3,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 18,74</t>
+          <t>-6,39; 8,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 14,41</t>
+          <t>-11,22; 1,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 3,6</t>
+          <t>-8,73; 5,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 10,82</t>
+          <t>-0,03; 11,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 6,35</t>
+          <t>-3,93; 6,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 2,51</t>
+          <t>-5,96; 2,9</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>253,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>178,23%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-30,82%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>9,34%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-65,65%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-33,33%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>253,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>178,23%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-33,05%</t>
+          <t>-22,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-32,58%</t>
+          <t>-25,32%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-74,57; 327,11</t>
+          <t>-13,44; 1450,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 154,89</t>
+          <t>-39,66; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-83,13; 214,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,06; —</t>
+          <t>-73,22; 301,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,62; 1354,97</t>
+          <t>-100,0; 144,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-84,01; 212,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,13; 367,07</t>
+          <t>-8,22; 378,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-56,92; 235,6</t>
+          <t>-53,95; 196,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-80,43; 94,42</t>
+          <t>-76,49; 116,55</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4,94</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,45</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-0,09</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>2,92</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>4,8</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-2,11</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,94</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,45</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,01</t>
+          <t>-1,05</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,06</t>
+          <t>-0,53</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 8,81</t>
+          <t>-1,35; 11,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 11,38</t>
+          <t>-5,87; 4,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 3,16</t>
+          <t>-4,92; 6,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 11,58</t>
+          <t>-2,99; 9,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 4,79</t>
+          <t>-1,59; 10,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 5,49</t>
+          <t>-6,27; 4,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 8,37</t>
+          <t>-0,33; 8,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 6,28</t>
+          <t>-1,67; 6,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 2,73</t>
+          <t>-4,43; 3,5</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>75,47%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-6,84%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-1,39%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>47,41%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>77,87%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-34,29%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>75,47%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-6,84%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>-17,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-16,6%</t>
+          <t>-8,34%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-34,66; 243,12</t>
+          <t>-18,76; 280,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-18,11; 321,58</t>
+          <t>-65,26; 127,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-79,44; 99,02</t>
+          <t>-58,76; 152,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 300,41</t>
+          <t>-34,61; 282,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-58,94; 125,17</t>
+          <t>-27,56; 281,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-58,12; 163,06</t>
+          <t>-76,07; 132,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 181,72</t>
+          <t>-6,46; 191,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,18; 140,21</t>
+          <t>-22,51; 152,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-57,5; 62,87</t>
+          <t>-54,5; 90,77</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>6,43</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,76</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3,57</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>5,1</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-0,17</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>4,82</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>6,43</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,76</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,92</t>
+          <t>4,67</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4,32</t>
+          <t>4,11</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 11,85</t>
+          <t>1,33; 13,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 4,04</t>
+          <t>-4,34; 2,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 12,13</t>
+          <t>-1,08; 9,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 13,67</t>
+          <t>-0,34; 11,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 2,59</t>
+          <t>-4,58; 4,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 11,35</t>
+          <t>-0,96; 11,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 10,59</t>
+          <t>1,93; 10,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 1,94</t>
+          <t>-2,95; 2,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 9,11</t>
+          <t>0,58; 8,64</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>369,69%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-43,67%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>204,94%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>227,67%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-7,46%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>215,18%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>369,69%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-43,67%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>225,3%</t>
+          <t>208,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>217,91%</t>
+          <t>206,85%</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-50,73; —</t>
+          <t>-35,92; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-50,12; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-24,45; —</t>
+          <t>-67,18; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-87,55; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 1422,62</t>
+          <t>19,74; 1476,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-13,77; 1145,25</t>
+          <t>-14,04; 1136,06</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-3,15</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,62</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-4,96</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-0,61</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-0,51</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,7</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-3,15</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,62</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-5,13</t>
+          <t>-0,48</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,98</t>
+          <t>-2,77</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 4,15</t>
+          <t>-9,59; 3,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 5,04</t>
+          <t>-7,57; 6,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 4,91</t>
+          <t>-11,26; 2,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 2,73</t>
+          <t>-5,88; 4,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 6,41</t>
+          <t>-5,73; 4,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 1,4</t>
+          <t>-5,81; 6,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 2,37</t>
+          <t>-6,12; 2,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 3,86</t>
+          <t>-5,23; 3,85</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 1,51</t>
+          <t>-7,13; 1,76</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-39,63%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-7,84%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-62,3%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-14,64%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-12,1%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-16,77%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-39,63%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-7,84%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-64,42%</t>
+          <t>-11,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-48,72%</t>
+          <t>-45,3%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 300,67</t>
+          <t>-83,58; 125,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-70,25; 143,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 345,9</t>
+          <t>-100,0; 117,04</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-87,72; 83,18</t>
+          <t>-100,0; 232,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-65,91; 146,86</t>
+          <t>-86,38; 410,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 77,77</t>
+          <t>-100,0; 499,79</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-74,21; 68,86</t>
+          <t>-72,46; 68,35</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-59,13; 101,08</t>
+          <t>-60,6; 106,7</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-83,33; 69,4</t>
+          <t>-85,06; 78,31</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>6,47</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3,56</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>7,85</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>7,34</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>6,09</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>4,15</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>6,47</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>3,56</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,28</t>
+          <t>4,1</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5,8</t>
+          <t>6,06</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 16,76</t>
+          <t>0,41; 14,94</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 15,17</t>
+          <t>-1,82; 9,84</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 12,67</t>
+          <t>1,46; 16,6</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,25; 15,19</t>
+          <t>-0,04; 17,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 9,79</t>
+          <t>-1,4; 16,65</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,34; 15,35</t>
+          <t>-2,97; 12,22</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,27; 13,11</t>
+          <t>1,76; 13,48</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 9,88</t>
+          <t>0,3; 10,82</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,64; 11,75</t>
+          <t>1,19; 12,28</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>436,43%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>239,84%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>529,04%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>230,5%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>191,15%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>130,26%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>436,43%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>239,84%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>490,87%</t>
+          <t>128,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>251,83%</t>
+          <t>262,94%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-48,24; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-73,28; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-80,41; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
+          <t>-62,46; —</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>-58,51; —</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 1482,28</t>
+          <t>-2,19; —</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-26,25; 1404,29</t>
+          <t>-33,92; 1326,63</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-15,37; 1356,7</t>
+          <t>-13,91; 1255,82</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>0,15</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-0,44</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>4,09</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>0,07</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-1,6</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>5,18</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>0,15</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-0,44</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,32</t>
+          <t>5,47</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4,69</t>
+          <t>4,76</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 5,48</t>
+          <t>-3,25; 5,69</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 1,99</t>
+          <t>-4,27; 5,08</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 13,7</t>
+          <t>-0,54; 11,61</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 4,82</t>
+          <t>-5,22; 5,87</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 4,84</t>
+          <t>-7,85; 1,21</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 11,17</t>
+          <t>-1,77; 13,16</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 3,79</t>
+          <t>-3,58; 3,4</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 2,07</t>
+          <t>-4,3; 2,02</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,09; 9,51</t>
+          <t>0,0; 9,52</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>7,13%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-20,63%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>192,23%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>2,53%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-57,56%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>186,22%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>7,13%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-20,63%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>203,04%</t>
+          <t>196,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>191,74%</t>
+          <t>194,61%</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-54,68; —</t>
+          <t>-55,29; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1888,22 +1888,22 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-71,39; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-85,93; 503,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 410,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-31,17; 915,67</t>
+          <t>-14,39; 1208,36</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-0,44</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-0,62</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>8,53</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>-1,35</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-1,91</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>4,36</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-0,44</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-0,62</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,87</t>
+          <t>4,64</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>6,22</t>
+          <t>6,67</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 2,61</t>
+          <t>-3,3; 2,47</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 1,64</t>
+          <t>-3,59; 2,27</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 10,13</t>
+          <t>3,82; 14,39</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 2,33</t>
+          <t>-5,53; 2,49</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 1,92</t>
+          <t>-6,04; 1,58</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,48; 13,17</t>
+          <t>-0,23; 10,34</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 1,58</t>
+          <t>-3,33; 1,36</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 1,0</t>
+          <t>-3,66; 1,09</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2,67; 10,05</t>
+          <t>3,0; 10,42</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-17,52%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-24,69%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>341,15%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>-28,06%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-39,84%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>90,84%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-17,52%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-24,69%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>314,77%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>171,63%</t>
+          <t>184,22%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-78,36; 105,15</t>
+          <t>-90,38; 269,25</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-85,19; 80,26</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 376,23</t>
+          <t>51,14; 1243,05</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-87,37; 287,76</t>
+          <t>-78,77; 101,22</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-88,93; 247,46</t>
+          <t>-82,55; 70,95</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>51,38; 1261,75</t>
+          <t>-8,42; 402,95</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-67,47; 72,21</t>
+          <t>-70,22; 60,34</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-72,09; 60,72</t>
+          <t>-72,76; 53,31</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>52,4; 457,23</t>
+          <t>54,17; 433,71</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-4,1</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-4,3</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>-2,92</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>-0,66</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>2,69</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-0,7</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-4,1</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>-4,3</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-2,91</t>
+          <t>-1,36</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-1,75</t>
+          <t>-2,1</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 2,77</t>
+          <t>-8,72; -0,04</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 6,65</t>
+          <t>-9,09; -0,08</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 2,96</t>
+          <t>-7,98; 1,84</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 0,01</t>
+          <t>-4,14; 2,75</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-8,54; -0,25</t>
+          <t>-1,21; 6,82</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 2,27</t>
+          <t>-4,67; 1,63</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 0,17</t>
+          <t>-5,37; 0,2</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 2,11</t>
+          <t>-3,74; 1,98</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 1,51</t>
+          <t>-5,01; 0,46</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-47,76%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-50,11%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>-34,02%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>-15,34%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>62,87%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-16,43%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-47,76%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>-50,11%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-33,86%</t>
+          <t>-31,89%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-27,11%</t>
+          <t>-32,39%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-70,24; 107,84</t>
+          <t>-76,31; 10,81</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-23,68; 259,06</t>
+          <t>-80,78; 0,82</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-68,25; 137,86</t>
+          <t>-71,47; 36,24</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-75,99; 6,13</t>
+          <t>-67,27; 122,63</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-75,7; 1,29</t>
+          <t>-22,35; 277,43</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-67,78; 44,96</t>
+          <t>-76,59; 79,52</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-64,82; 6,6</t>
+          <t>-65,26; 5,53</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-45,74; 47,23</t>
+          <t>-47,04; 42,23</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-57,4; 30,86</t>
+          <t>-63,23; 13,5</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>1,14</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-0,58</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>1,52</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>0,97</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>0,8</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>1,16</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>1,14</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>-0,58</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,36</t>
+          <t>1,38</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1,28</t>
+          <t>1,46</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 2,78</t>
+          <t>-0,66; 3,11</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 2,64</t>
+          <t>-2,34; 1,18</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 3,06</t>
+          <t>-0,35; 3,78</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 3,16</t>
+          <t>-0,95; 3,02</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 1,15</t>
+          <t>-1,0; 2,54</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 3,45</t>
+          <t>-0,47; 3,49</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 2,49</t>
+          <t>-0,28; 2,42</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 1,37</t>
+          <t>-1,15; 1,43</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 2,71</t>
+          <t>0,05; 2,94</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>22,88%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-11,68%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>30,34%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>21,79%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>17,84%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>26,01%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>22,88%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>-11,68%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>30,8%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-18,6; 78,53</t>
+          <t>-11,32; 73,41</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-18,79; 74,82</t>
+          <t>-38,8; 30,54</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-16,25; 84,96</t>
+          <t>-6,34; 88,09</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-12,7; 75,61</t>
+          <t>-17,93; 85,0</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-41,96; 27,4</t>
+          <t>-18,98; 69,03</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 84,85</t>
+          <t>-9,31; 102,35</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 59,6</t>
+          <t>-5,8; 57,89</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-23,0; 33,84</t>
+          <t>-21,97; 34,04</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 65,8</t>
+          <t>0,28; 70,19</t>
         </is>
       </c>
     </row>
